--- a/RhynieGuildStructure.xlsx
+++ b/RhynieGuildStructure.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tannerfrank/Dropbox/Work/Devonian terr ecosystems/EcolNetworks/RhynieWebRepo/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334E4D07-7CAA-8B45-AC52-8FA729F4BB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="16000" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Guilds" sheetId="1" r:id="rId4"/>
-    <sheet name="Guild composition" sheetId="2" r:id="rId5"/>
+    <sheet name="Guilds" sheetId="1" r:id="rId1"/>
+    <sheet name="Guild composition" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="250">
   <si>
     <t>guild_no</t>
   </si>
@@ -236,9 +245,6 @@
     <t>Trigonotarbida</t>
   </si>
   <si>
-    <t>22,25,26</t>
-  </si>
-  <si>
     <t>24?,11,10,9?,8</t>
   </si>
   <si>
@@ -488,9 +494,6 @@
     <t>Veterisphaera dumosa</t>
   </si>
   <si>
-    <t>Prototaxites</t>
-  </si>
-  <si>
     <t>Glomites rhyniensis</t>
   </si>
   <si>
@@ -762,33 +765,26 @@
   </si>
   <si>
     <t>scolecodont</t>
+  </si>
+  <si>
+    <t>Prototaxites taiti</t>
+  </si>
+  <si>
+    <t>22,23,25,26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i val="1"/>
+      <i/>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Aptos Narrow"/>
@@ -926,92 +922,59 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+  <cellXfs count="28">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1020,24 +983,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office Theme">
       <a:dk1>
@@ -1239,7 +1263,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1257,7 +1281,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1286,7 +1310,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1311,7 +1335,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1336,7 +1360,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1361,7 +1385,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1386,7 +1410,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1411,7 +1435,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1436,7 +1460,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1461,7 +1485,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1486,7 +1510,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1499,9 +1523,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1518,7 +1548,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1536,7 +1566,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1561,7 +1591,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1586,7 +1616,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1611,7 +1641,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1636,7 +1666,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1661,7 +1691,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1686,7 +1716,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1711,7 +1741,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1736,7 +1766,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1761,7 +1791,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1774,9 +1804,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1790,7 +1826,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1808,7 +1844,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1837,7 +1873,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1862,7 +1898,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1887,7 +1923,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1912,7 +1948,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1937,7 +1973,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1962,7 +1998,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1987,7 +2023,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2012,7 +2048,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2037,7 +2073,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2050,81 +2086,88 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I47"/>
-  <sheetFormatPr defaultColWidth="10.8333" defaultRowHeight="16" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.8516" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.8516" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.85156" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.83203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="23" style="1" customWidth="1"/>
-    <col min="6" max="6" width="26.6719" style="1" customWidth="1"/>
-    <col min="7" max="7" width="42.1719" style="1" customWidth="1"/>
-    <col min="8" max="9" width="10.8516" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.8516" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="42.1640625" style="1" customWidth="1"/>
+    <col min="8" max="10" width="10.83203125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s" s="2">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="2">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="2">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="2">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="2">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="2">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="2">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1">
+    <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s" s="2">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
       </c>
-      <c r="E2" t="s" s="2">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s" s="2">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="3">
@@ -2134,26 +2177,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="17" customHeight="1">
+    <row r="3" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s" s="4">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s" s="4">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
       </c>
-      <c r="E3" t="s" s="2">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s" s="2">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" t="s" s="2">
+      <c r="G3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="3">
@@ -2163,26 +2206,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1">
+    <row r="4" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" t="s" s="4">
+      <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s" s="4">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
       </c>
-      <c r="E4" t="s" s="2">
+      <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s" s="2">
+      <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G4" t="s" s="2">
+      <c r="G4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H4" s="3">
@@ -2192,26 +2235,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1">
+    <row r="5" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s" s="4">
+      <c r="B5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s" s="4">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" t="s" s="2">
+      <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F5" t="s" s="2">
+      <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G5" t="s" s="2">
+      <c r="G5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="3">
@@ -2221,26 +2264,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="17" customHeight="1">
+    <row r="6" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" t="s" s="4">
+      <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s" s="4">
+      <c r="C6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
       </c>
-      <c r="E6" t="s" s="2">
+      <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F6" t="s" s="2">
+      <c r="F6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G6" t="s" s="2">
+      <c r="G6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H6" s="3">
@@ -2250,26 +2293,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="17" customHeight="1">
+    <row r="7" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" t="s" s="4">
+      <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s" s="4">
+      <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
       </c>
-      <c r="E7" t="s" s="2">
+      <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F7" t="s" s="2">
+      <c r="F7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G7" t="s" s="2">
+      <c r="G7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H7" s="3">
@@ -2279,26 +2322,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="17" customHeight="1">
+    <row r="8" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" t="s" s="2">
+      <c r="C8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
       </c>
-      <c r="E8" t="s" s="2">
+      <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" t="s" s="2">
+      <c r="F8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G8" t="s" s="2">
+      <c r="G8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H8" s="3">
@@ -2308,24 +2351,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="17" customHeight="1">
+    <row r="9" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="3">
         <v>1</v>
       </c>
-      <c r="E9" t="s" s="2">
+      <c r="E9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F9" t="s" s="2">
+      <c r="F9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G9" t="s" s="2">
+      <c r="G9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="3">
@@ -2335,11 +2378,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="17" customHeight="1">
+    <row r="10" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="5"/>
@@ -2349,10 +2392,10 @@
       <c r="E10" s="3">
         <v>1</v>
       </c>
-      <c r="F10" t="s" s="2">
+      <c r="F10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G10" t="s" s="2">
+      <c r="G10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H10" s="3">
@@ -2362,21 +2405,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="17" customHeight="1">
+    <row r="11" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="3">
         <v>1</v>
       </c>
-      <c r="E11" t="s" s="2">
+      <c r="E11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F11" t="s" s="2">
+      <c r="F11" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G11" s="5"/>
@@ -2387,14 +2430,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="17" customHeight="1">
+    <row r="12" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" t="s" s="2">
+      <c r="B12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C12" t="s" s="2">
+      <c r="C12" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D12" s="3">
@@ -2414,21 +2457,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="17" customHeight="1">
+    <row r="13" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" t="s" s="2">
+      <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="3">
         <v>3</v>
       </c>
-      <c r="E13" t="s" s="2">
+      <c r="E13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F13" t="s" s="2">
+      <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G13" s="2"/>
@@ -2439,21 +2482,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="17" customHeight="1">
+    <row r="14" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" t="s" s="2">
+      <c r="B14" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="3">
         <v>2</v>
       </c>
-      <c r="E14" t="s" s="2">
+      <c r="E14" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F14" t="s" s="2">
+      <c r="F14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G14" s="2"/>
@@ -2464,21 +2507,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="17" customHeight="1">
+    <row r="15" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" t="s" s="2">
+      <c r="B15" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="3">
         <v>3</v>
       </c>
-      <c r="E15" t="s" s="2">
+      <c r="E15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F15" t="s" s="2">
+      <c r="F15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G15" s="2"/>
@@ -2489,21 +2532,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="17" customHeight="1">
+    <row r="16" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" t="s" s="2">
+      <c r="B16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="3">
         <v>3</v>
       </c>
-      <c r="E16" t="s" s="2">
+      <c r="E16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F16" t="s" s="2">
+      <c r="F16" s="2" t="s">
         <v>39</v>
       </c>
       <c r="G16" s="2"/>
@@ -2514,24 +2557,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="17" customHeight="1">
+    <row r="17" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" t="s" s="2">
+      <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C17" t="s" s="2">
+      <c r="C17" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" t="s" s="2">
+      <c r="F17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G17" t="s" s="2">
+      <c r="G17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="H17" s="3">
@@ -2541,21 +2584,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="17" customHeight="1">
+    <row r="18" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" t="s" s="2">
+      <c r="B18" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="3">
         <v>1</v>
       </c>
-      <c r="E18" t="s" s="2">
+      <c r="E18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F18" t="s" s="2">
+      <c r="F18" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G18" s="2"/>
@@ -2566,21 +2609,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="17" customHeight="1">
+    <row r="19" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" t="s" s="2">
+      <c r="B19" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="3">
         <v>3</v>
       </c>
-      <c r="E19" t="s" s="2">
+      <c r="E19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F19" t="s" s="2">
+      <c r="F19" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G19" s="2"/>
@@ -2591,21 +2634,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="17" customHeight="1">
+    <row r="20" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B20" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="3">
         <v>1</v>
       </c>
-      <c r="E20" t="s" s="2">
+      <c r="E20" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F20" t="s" s="2">
+      <c r="F20" s="2" t="s">
         <v>50</v>
       </c>
       <c r="G20" s="2"/>
@@ -2616,24 +2659,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="17" customHeight="1">
+    <row r="21" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" t="s" s="2">
+      <c r="B21" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C21" t="s" s="2">
+      <c r="C21" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D21" s="3">
         <v>2</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" t="s" s="2">
+      <c r="F21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G21" t="s" s="2">
+      <c r="G21" s="2" t="s">
         <v>43</v>
       </c>
       <c r="H21" s="3">
@@ -2643,24 +2686,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="17" customHeight="1">
+    <row r="22" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" t="s" s="2">
+      <c r="B22" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C22" t="s" s="2">
+      <c r="C22" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D22" s="3">
         <v>7</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" t="s" s="2">
+      <c r="F22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G22" t="s" s="2">
+      <c r="G22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="H22" s="3">
@@ -2670,21 +2713,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="17" customHeight="1">
+    <row r="23" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" t="s" s="2">
+      <c r="B23" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="3">
         <v>1</v>
       </c>
-      <c r="E23" t="s" s="2">
+      <c r="E23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F23" t="s" s="2">
+      <c r="F23" s="2" t="s">
         <v>58</v>
       </c>
       <c r="G23" s="2"/>
@@ -2695,26 +2738,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="17" customHeight="1">
+    <row r="24" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" t="s" s="2">
+      <c r="B24" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C24" t="s" s="2">
+      <c r="C24" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D24" s="3">
         <v>1</v>
       </c>
-      <c r="E24" t="s" s="2">
+      <c r="E24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F24" t="s" s="2">
+      <c r="F24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G24" t="s" s="2">
+      <c r="G24" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H24" s="3">
@@ -2724,26 +2767,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="17" customHeight="1">
+    <row r="25" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" t="s" s="2">
+      <c r="B25" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C25" t="s" s="2">
+      <c r="C25" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D25" s="3">
         <v>2</v>
       </c>
-      <c r="E25" t="s" s="2">
+      <c r="E25" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F25" t="s" s="2">
+      <c r="F25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G25" t="s" s="2">
+      <c r="G25" s="2" t="s">
         <v>67</v>
       </c>
       <c r="H25" s="3">
@@ -2753,24 +2796,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="17" customHeight="1">
+    <row r="26" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" t="s" s="2">
+      <c r="B26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C26" t="s" s="2">
+      <c r="C26" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D26" s="3">
         <v>2</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" t="s" s="2">
+      <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G26" t="s" s="2">
+      <c r="G26" s="2" t="s">
         <v>71</v>
       </c>
       <c r="H26" s="3">
@@ -2780,25 +2823,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="17" customHeight="1">
+    <row r="27" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" t="s" s="2">
+      <c r="B27" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C27" t="s" s="2">
+      <c r="C27" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D27" s="3">
         <v>3</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" t="s" s="2">
+      <c r="F27" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="H27" s="3">
         <v>1</v>
@@ -2807,25 +2850,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="17" customHeight="1">
+    <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" t="s" s="2">
+      <c r="B28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="D28" s="3">
         <v>5</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" t="s" s="2">
+      <c r="F28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="H28" s="3">
         <v>1</v>
@@ -2834,25 +2877,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="17" customHeight="1">
+    <row r="29" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" t="s" s="2">
+      <c r="B29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="D29" s="3">
-        <v>1</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -2861,25 +2904,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="17" customHeight="1">
+    <row r="30" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" t="s" s="2">
-        <v>82</v>
+      <c r="B30" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="3">
         <v>1</v>
       </c>
-      <c r="E30" t="s" s="2">
+      <c r="E30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F30" t="s" s="2">
+      <c r="G30" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="H30" s="3">
         <v>0</v>
@@ -2888,19 +2931,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" ht="17" customHeight="1">
+    <row r="31" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" t="s" s="2">
-        <v>86</v>
+      <c r="B31" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="3">
         <v>1</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" t="s" s="2">
+      <c r="F31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G31" s="5"/>
@@ -2911,22 +2954,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" ht="17" customHeight="1">
+    <row r="32" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" t="s" s="2">
-        <v>87</v>
+      <c r="B32" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="3">
         <v>1</v>
       </c>
-      <c r="E32" t="s" s="2">
+      <c r="E32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="F32" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="3">
@@ -2936,19 +2979,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" ht="17" customHeight="1">
+    <row r="33" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" t="s" s="2">
-        <v>90</v>
+      <c r="B33" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="3">
         <v>1</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" t="s" s="2">
+      <c r="F33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G33" s="5"/>
@@ -2959,21 +3002,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="17" customHeight="1">
+    <row r="34" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" t="s" s="2">
+      <c r="B34" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="D34" s="3">
         <v>5</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" t="s" s="2">
+      <c r="F34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G34" s="5"/>
@@ -2984,21 +3027,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1">
+    <row r="35" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="C35" t="s" s="2">
+      <c r="B35" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="C35" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="D35" s="3">
         <v>1</v>
       </c>
       <c r="E35" s="5"/>
-      <c r="F35" t="s" s="2">
+      <c r="F35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G35" s="5"/>
@@ -3009,21 +3052,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="17" customHeight="1">
+    <row r="36" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>92</v>
+      <c r="B36" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="D36" s="3">
         <v>5</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" t="s" s="2">
+      <c r="F36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G36" s="5"/>
@@ -3034,21 +3077,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="17" customHeight="1">
+    <row r="37" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>92</v>
+      <c r="B37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="D37" s="3">
         <v>4</v>
       </c>
       <c r="E37" s="5"/>
-      <c r="F37" t="s" s="2">
+      <c r="F37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G37" s="5"/>
@@ -3059,21 +3102,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" ht="17" customHeight="1">
+    <row r="38" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" t="s" s="2">
+      <c r="B38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C38" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="D38" s="3">
         <v>1</v>
       </c>
       <c r="E38" s="5"/>
-      <c r="F38" t="s" s="2">
+      <c r="F38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G38" s="5"/>
@@ -3084,21 +3127,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" ht="17" customHeight="1">
+    <row r="39" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" t="s" s="2">
+      <c r="B39" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="D39" s="3">
         <v>3</v>
       </c>
       <c r="E39" s="5"/>
-      <c r="F39" t="s" s="2">
+      <c r="F39" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G39" s="5"/>
@@ -3109,14 +3152,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" ht="17" customHeight="1">
+    <row r="40" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="C40" t="s" s="2">
+      <c r="B40" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D40" s="3">
@@ -3136,27 +3179,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" ht="17" customHeight="1">
+    <row r="41" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" t="s" s="2">
+      <c r="B41" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="3">
+        <v>1</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C41" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D41" s="3">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s" s="2">
+      <c r="F41" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F41" t="s" s="2">
+      <c r="G41" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="H41" s="3">
         <v>0</v>
@@ -3165,25 +3208,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" ht="17" customHeight="1">
+    <row r="42" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" t="s" s="2">
+      <c r="B42" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" s="3">
+        <v>1</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C42" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D42" s="3">
-        <v>1</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
+      <c r="G42" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -3192,26 +3235,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" ht="17" customHeight="1">
+    <row r="43" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" t="s" s="2">
+      <c r="B43" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C43" t="s" s="2">
+      <c r="D43" s="3">
+        <v>1</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D43" s="3">
-        <v>1</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
+      <c r="G43" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>111</v>
-      </c>
       <c r="H43" s="3">
         <v>1</v>
       </c>
@@ -3219,25 +3262,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" ht="17" customHeight="1">
+    <row r="44" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" t="s" s="2">
+      <c r="B44" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="D44" s="3">
         <v>2</v>
       </c>
       <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
+      <c r="F44" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="H44" s="3">
         <v>0</v>
@@ -3246,27 +3289,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" ht="17" customHeight="1">
+    <row r="45" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" t="s" s="2">
+      <c r="B45" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="3">
+        <v>1</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C45" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="D45" s="3">
-        <v>1</v>
-      </c>
-      <c r="E45" t="s" s="2">
+      <c r="F45" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F45" t="s" s="2">
+      <c r="G45" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
@@ -3275,25 +3318,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" ht="17" customHeight="1">
+    <row r="46" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" t="s" s="2">
+      <c r="B46" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="D46" s="3">
         <v>2</v>
       </c>
       <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
+      <c r="F46" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="H46" s="3">
         <v>0</v>
@@ -3302,25 +3345,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" ht="17" customHeight="1">
+    <row r="47" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>46</v>
       </c>
-      <c r="B47" t="s" s="2">
+      <c r="B47" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C47" t="s" s="2">
+      <c r="D47" s="3">
+        <v>1</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D47" s="3">
-        <v>1</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
+      <c r="G47" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="H47" s="3">
         <v>0</v>
@@ -3331,7 +3374,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -3339,1634 +3382,1631 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E151"/>
-  <sheetFormatPr defaultColWidth="10.8333" defaultRowHeight="16" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.8516" style="6" customWidth="1"/>
-    <col min="2" max="2" width="29.3516" style="6" customWidth="1"/>
-    <col min="3" max="3" width="25.3516" style="6" customWidth="1"/>
-    <col min="4" max="5" width="10.8516" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="10.8516" style="6" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" style="1" customWidth="1"/>
+    <col min="4" max="6" width="10.83203125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1">
-      <c r="A1" t="s" s="7">
+    <row r="1" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B1" t="s" s="7">
+      <c r="C1" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C1" t="s" s="7">
+      <c r="D1" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D1" t="s" s="7">
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="2" ht="17" customHeight="1">
-      <c r="A2" s="8">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s" s="7">
+      <c r="D3" s="8"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="9"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="9"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="9"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="7">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="9"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="7">
+        <v>2</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="11">
+        <v>8</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="7">
         <v>9</v>
       </c>
-      <c r="C2" s="8">
-        <v>1</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" t="s" s="7">
-        <v>132</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="8">
+      <c r="B20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="11">
+        <v>10</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="13">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14"/>
+      <c r="E22" s="5"/>
+    </row>
+    <row r="23" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="7">
+        <v>11</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="7">
+        <v>14</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E30" s="5"/>
+    </row>
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="8"/>
+      <c r="E31" s="5"/>
+    </row>
+    <row r="32" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="5"/>
+    </row>
+    <row r="33" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="D34" s="27"/>
+      <c r="E34" s="5"/>
+    </row>
+    <row r="35" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="8"/>
+      <c r="E35" s="5"/>
+    </row>
+    <row r="36" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="5"/>
+    </row>
+    <row r="37" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" s="5"/>
+    </row>
+    <row r="38" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" s="5"/>
+    </row>
+    <row r="39" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="7">
+        <v>12</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="7">
+        <v>3</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="5"/>
+    </row>
+    <row r="40" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="9"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="8"/>
+      <c r="E40" s="5"/>
+    </row>
+    <row r="41" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="9"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="5"/>
+    </row>
+    <row r="42" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="9"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" s="8"/>
+      <c r="E42" s="5"/>
+    </row>
+    <row r="43" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="7">
+        <v>13</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="7">
         <v>2</v>
       </c>
-      <c r="B4" t="s" s="4">
-        <v>11</v>
-      </c>
-      <c r="C4" s="8">
-        <v>1</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="10"/>
-      <c r="B5" s="4"/>
-      <c r="C5" t="s" s="7">
-        <v>133</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="8">
+      <c r="D43" s="8"/>
+      <c r="E43" s="5"/>
+    </row>
+    <row r="44" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="9"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" s="8"/>
+      <c r="E44" s="5"/>
+    </row>
+    <row r="45" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="9"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="D45" s="8"/>
+      <c r="E45" s="5"/>
+    </row>
+    <row r="46" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="7">
+        <v>14</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="7">
         <v>3</v>
       </c>
-      <c r="B6" t="s" s="4">
-        <v>13</v>
-      </c>
-      <c r="C6" s="8">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="10"/>
-      <c r="B7" s="4"/>
-      <c r="C7" t="s" s="11">
-        <v>134</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="8">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s" s="4">
-        <v>14</v>
-      </c>
-      <c r="C8" s="8">
-        <v>1</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="10"/>
-      <c r="B9" s="4"/>
-      <c r="C9" t="s" s="11">
-        <v>135</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="8">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s" s="4">
+      <c r="D46" s="8"/>
+      <c r="E46" s="5"/>
+    </row>
+    <row r="47" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="9"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D47" s="8"/>
+      <c r="E47" s="5"/>
+    </row>
+    <row r="48" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="9"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D48" s="8"/>
+      <c r="E48" s="5"/>
+    </row>
+    <row r="49" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="9"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D49" s="8"/>
+      <c r="E49" s="5"/>
+    </row>
+    <row r="50" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="7">
         <v>15</v>
       </c>
-      <c r="C10" s="8">
-        <v>1</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="4"/>
-      <c r="C11" t="s" s="11">
-        <v>136</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="8">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s" s="4">
+      <c r="B50" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" s="7">
+        <v>3</v>
+      </c>
+      <c r="D50" s="8"/>
+      <c r="E50" s="5"/>
+    </row>
+    <row r="51" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="9"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D51" s="8"/>
+      <c r="E51" s="5"/>
+    </row>
+    <row r="52" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="9"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" s="8"/>
+      <c r="E52" s="5"/>
+    </row>
+    <row r="53" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="9"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D53" s="8"/>
+      <c r="E53" s="5"/>
+    </row>
+    <row r="54" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="7">
         <v>16</v>
       </c>
-      <c r="C12" s="8">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="7"/>
-      <c r="C13" t="s" s="11">
-        <v>137</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="8">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s" s="7">
+      <c r="B54" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="7">
+        <v>1</v>
+      </c>
+      <c r="D54" s="8"/>
+      <c r="E54" s="5"/>
+    </row>
+    <row r="55" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E55" s="5"/>
+    </row>
+    <row r="56" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="7">
         <v>17</v>
       </c>
-      <c r="C14" s="8">
+      <c r="B56" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C56" s="7">
+        <v>1</v>
+      </c>
+      <c r="D56" s="8"/>
+      <c r="E56" s="5"/>
+    </row>
+    <row r="57" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="9"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D57" s="8"/>
+      <c r="E57" s="5"/>
+    </row>
+    <row r="58" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="7">
+        <v>18</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C58" s="7">
+        <v>3</v>
+      </c>
+      <c r="D58" s="8"/>
+      <c r="E58" s="5"/>
+    </row>
+    <row r="59" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="9"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E59" s="5"/>
+    </row>
+    <row r="60" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="9"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" s="5"/>
+    </row>
+    <row r="61" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="9"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D61" s="8"/>
+      <c r="E61" s="5"/>
+    </row>
+    <row r="62" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="7">
+        <v>19</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C62" s="7">
+        <v>1</v>
+      </c>
+      <c r="D62" s="8"/>
+      <c r="E62" s="5"/>
+    </row>
+    <row r="63" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="9"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E63" s="5"/>
+    </row>
+    <row r="64" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="7">
+        <v>20</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C64" s="7">
         <v>2</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" t="s" s="11">
-        <v>138</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" t="s" s="11">
-        <v>139</v>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="12">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s" s="13">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s" s="11">
-        <v>65</v>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" t="s" s="11">
-        <v>140</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="8">
-        <v>9</v>
-      </c>
-      <c r="B20" t="s" s="7">
-        <v>20</v>
-      </c>
-      <c r="C20" s="8">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="5"/>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" t="s" s="11">
-        <v>141</v>
-      </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="12">
-        <v>10</v>
-      </c>
-      <c r="B22" t="s" s="13">
-        <v>23</v>
-      </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" t="s" s="11">
-        <v>142</v>
-      </c>
-      <c r="D23" t="s" s="11">
-        <v>143</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="8">
-        <v>11</v>
-      </c>
-      <c r="B24" t="s" s="7">
-        <v>26</v>
-      </c>
-      <c r="C24" s="8">
-        <v>14</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" t="s" s="11">
-        <v>144</v>
-      </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" t="s" s="11">
-        <v>145</v>
-      </c>
-      <c r="D26" t="s" s="7">
-        <v>146</v>
-      </c>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" t="s" s="11">
-        <v>147</v>
-      </c>
-      <c r="D27" t="s" s="11">
-        <v>146</v>
-      </c>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" t="s" s="11">
-        <v>148</v>
-      </c>
-      <c r="D28" t="s" s="11">
-        <v>146</v>
-      </c>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" t="s" s="11">
-        <v>149</v>
-      </c>
-      <c r="D29" t="s" s="11">
-        <v>146</v>
-      </c>
-      <c r="E29" s="5"/>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" t="s" s="11">
-        <v>150</v>
-      </c>
-      <c r="D30" t="s" s="11">
-        <v>146</v>
-      </c>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" t="s" s="11">
-        <v>151</v>
-      </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="5"/>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" t="s" s="11">
-        <v>152</v>
-      </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="5"/>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" t="s" s="11">
-        <v>153</v>
-      </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="5"/>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" t="s" s="11">
-        <v>154</v>
-      </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" t="s" s="11">
-        <v>155</v>
-      </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="5"/>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" t="s" s="11">
-        <v>156</v>
-      </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="5"/>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" t="s" s="11">
-        <v>157</v>
-      </c>
-      <c r="D37" t="s" s="7">
-        <v>146</v>
-      </c>
-      <c r="E37" s="5"/>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" t="s" s="11">
-        <v>158</v>
-      </c>
-      <c r="D38" t="s" s="7">
-        <v>146</v>
-      </c>
-      <c r="E38" s="5"/>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="8">
-        <v>12</v>
-      </c>
-      <c r="B39" t="s" s="7">
-        <v>28</v>
-      </c>
-      <c r="C39" s="8">
-        <v>3</v>
-      </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="5"/>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="10"/>
-      <c r="B40" s="7"/>
-      <c r="C40" t="s" s="11">
-        <v>159</v>
-      </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="5"/>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="10"/>
-      <c r="B41" s="7"/>
-      <c r="C41" t="s" s="11">
-        <v>160</v>
-      </c>
-      <c r="D41" s="9"/>
-      <c r="E41" s="5"/>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="10"/>
-      <c r="B42" s="7"/>
-      <c r="C42" t="s" s="11">
-        <v>161</v>
-      </c>
-      <c r="D42" s="9"/>
-      <c r="E42" s="5"/>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="8">
-        <v>13</v>
-      </c>
-      <c r="B43" t="s" s="7">
-        <v>31</v>
-      </c>
-      <c r="C43" s="8">
-        <v>2</v>
-      </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="5"/>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="10"/>
-      <c r="B44" s="7"/>
-      <c r="C44" t="s" s="16">
-        <v>162</v>
-      </c>
-      <c r="D44" s="9"/>
-      <c r="E44" s="5"/>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="10"/>
-      <c r="B45" s="7"/>
-      <c r="C45" t="s" s="11">
-        <v>163</v>
-      </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="5"/>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="8">
-        <v>14</v>
-      </c>
-      <c r="B46" t="s" s="7">
-        <v>34</v>
-      </c>
-      <c r="C46" s="8">
-        <v>3</v>
-      </c>
-      <c r="D46" s="9"/>
-      <c r="E46" s="5"/>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="10"/>
-      <c r="B47" s="7"/>
-      <c r="C47" t="s" s="16">
-        <v>164</v>
-      </c>
-      <c r="D47" s="9"/>
-      <c r="E47" s="5"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="10"/>
-      <c r="B48" s="7"/>
-      <c r="C48" t="s" s="11">
-        <v>165</v>
-      </c>
-      <c r="D48" s="9"/>
-      <c r="E48" s="5"/>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="10"/>
-      <c r="B49" s="7"/>
-      <c r="C49" t="s" s="11">
-        <v>166</v>
-      </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="5"/>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="8">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s" s="7">
-        <v>37</v>
-      </c>
-      <c r="C50" s="8">
-        <v>3</v>
-      </c>
-      <c r="D50" s="9"/>
-      <c r="E50" s="5"/>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="10"/>
-      <c r="B51" s="7"/>
-      <c r="C51" t="s" s="11">
-        <v>167</v>
-      </c>
-      <c r="D51" s="9"/>
-      <c r="E51" s="5"/>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="10"/>
-      <c r="B52" s="7"/>
-      <c r="C52" t="s" s="11">
-        <v>168</v>
-      </c>
-      <c r="D52" s="9"/>
-      <c r="E52" s="5"/>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="10"/>
-      <c r="B53" s="7"/>
-      <c r="C53" t="s" s="11">
-        <v>169</v>
-      </c>
-      <c r="D53" s="9"/>
-      <c r="E53" s="5"/>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="8">
-        <v>16</v>
-      </c>
-      <c r="B54" t="s" s="7">
-        <v>40</v>
-      </c>
-      <c r="C54" s="8">
-        <v>1</v>
-      </c>
-      <c r="D54" s="9"/>
-      <c r="E54" s="5"/>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" t="s" s="11">
-        <v>170</v>
-      </c>
-      <c r="D55" t="s" s="11">
-        <v>171</v>
-      </c>
-      <c r="E55" s="5"/>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="8">
-        <v>17</v>
-      </c>
-      <c r="B56" t="s" s="7">
-        <v>44</v>
-      </c>
-      <c r="C56" s="8">
-        <v>1</v>
-      </c>
-      <c r="D56" s="9"/>
-      <c r="E56" s="5"/>
-    </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="10"/>
-      <c r="B57" s="7"/>
-      <c r="C57" t="s" s="11">
-        <v>172</v>
-      </c>
-      <c r="D57" s="9"/>
-      <c r="E57" s="5"/>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="8">
-        <v>18</v>
-      </c>
-      <c r="B58" t="s" s="7">
-        <v>46</v>
-      </c>
-      <c r="C58" s="8">
-        <v>3</v>
-      </c>
-      <c r="D58" s="9"/>
-      <c r="E58" s="5"/>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="10"/>
-      <c r="B59" s="7"/>
-      <c r="C59" t="s" s="11">
-        <v>173</v>
-      </c>
-      <c r="D59" t="s" s="7">
-        <v>146</v>
-      </c>
-      <c r="E59" s="5"/>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="10"/>
-      <c r="B60" s="7"/>
-      <c r="C60" t="s" s="11">
-        <v>174</v>
-      </c>
-      <c r="D60" s="9"/>
-      <c r="E60" s="5"/>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="10"/>
-      <c r="B61" s="7"/>
-      <c r="C61" t="s" s="11">
-        <v>175</v>
-      </c>
-      <c r="D61" s="9"/>
-      <c r="E61" s="5"/>
-    </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="8">
-        <v>19</v>
-      </c>
-      <c r="B62" t="s" s="7">
-        <v>48</v>
-      </c>
-      <c r="C62" s="8">
-        <v>1</v>
-      </c>
-      <c r="D62" s="9"/>
-      <c r="E62" s="5"/>
-    </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="10"/>
-      <c r="B63" s="7"/>
-      <c r="C63" t="s" s="11">
+      <c r="D64" s="8"/>
+      <c r="E64" s="5"/>
+    </row>
+    <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="D63" t="s" s="11">
-        <v>146</v>
-      </c>
-      <c r="E63" s="5"/>
-    </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="8">
-        <v>20</v>
-      </c>
-      <c r="B64" t="s" s="7">
-        <v>177</v>
-      </c>
-      <c r="C64" s="8">
-        <v>2</v>
-      </c>
-      <c r="D64" s="9"/>
-      <c r="E64" s="5"/>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="9"/>
-      <c r="B65" s="9"/>
-      <c r="C65" t="s" s="11">
-        <v>178</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
     </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="9"/>
-      <c r="B66" s="9"/>
-      <c r="C66" t="s" s="11">
+    <row r="66" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E66" s="5"/>
+    </row>
+    <row r="67" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="7">
+        <v>21</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="7">
+        <v>7</v>
+      </c>
+      <c r="D67" s="8"/>
+      <c r="E67" s="5"/>
+    </row>
+    <row r="68" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D68" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D66" t="s" s="11">
-        <v>146</v>
-      </c>
-      <c r="E66" s="5"/>
-    </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="8">
-        <v>21</v>
-      </c>
-      <c r="B67" t="s" s="7">
-        <v>54</v>
-      </c>
-      <c r="C67" s="8">
-        <v>7</v>
-      </c>
-      <c r="D67" s="9"/>
-      <c r="E67" s="5"/>
-    </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="9"/>
-      <c r="B68" s="9"/>
-      <c r="C68" t="s" s="11">
+      <c r="E68" s="5"/>
+    </row>
+    <row r="69" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="D68" t="s" s="11">
+      <c r="D69" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E69" s="5"/>
+    </row>
+    <row r="70" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="E68" s="5"/>
-    </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="9"/>
-      <c r="B69" s="9"/>
-      <c r="C69" t="s" s="11">
+      <c r="D70" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E70" s="5"/>
+    </row>
+    <row r="71" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D69" t="s" s="13">
-        <v>181</v>
-      </c>
-      <c r="E69" s="5"/>
-    </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="9"/>
-      <c r="B70" s="9"/>
-      <c r="C70" t="s" s="11">
+      <c r="D71" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E71" s="5"/>
+    </row>
+    <row r="72" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="8"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D70" t="s" s="7">
-        <v>181</v>
-      </c>
-      <c r="E70" s="5"/>
-    </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="9"/>
-      <c r="B71" s="9"/>
-      <c r="C71" t="s" s="11">
+      <c r="D72" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D71" t="s" s="13">
-        <v>181</v>
-      </c>
-      <c r="E71" s="5"/>
-    </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="9"/>
-      <c r="B72" s="9"/>
-      <c r="C72" t="s" s="11">
+      <c r="E72" s="5"/>
+    </row>
+    <row r="73" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="8"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D72" t="s" s="7">
+      <c r="D73" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E72" s="5"/>
-    </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="9"/>
-      <c r="B73" s="9"/>
-      <c r="C73" t="s" s="11">
+      <c r="E73" s="5"/>
+    </row>
+    <row r="74" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="8"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D73" t="s" s="7">
+      <c r="D74" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="E73" s="5"/>
-    </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="9"/>
-      <c r="B74" s="9"/>
-      <c r="C74" t="s" s="11">
+      <c r="E74" s="5"/>
+    </row>
+    <row r="75" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="7">
+        <v>22</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="7">
+        <v>1</v>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="5"/>
+    </row>
+    <row r="76" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="9"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="D74" t="s" s="7">
+      <c r="D76" s="8"/>
+      <c r="E76" s="5"/>
+    </row>
+    <row r="77" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="7">
+        <v>23</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="E74" s="5"/>
-    </row>
-    <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="8">
-        <v>22</v>
-      </c>
-      <c r="B75" t="s" s="7">
-        <v>57</v>
-      </c>
-      <c r="C75" s="8">
-        <v>1</v>
-      </c>
-      <c r="D75" s="9"/>
-      <c r="E75" s="5"/>
-    </row>
-    <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="10"/>
-      <c r="B76" s="7"/>
-      <c r="C76" t="s" s="16">
+      <c r="C77" s="7">
+        <v>1</v>
+      </c>
+      <c r="D77" s="8"/>
+      <c r="E77" s="5"/>
+    </row>
+    <row r="78" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="8"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D76" s="9"/>
-      <c r="E76" s="5"/>
-    </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="8">
-        <v>23</v>
-      </c>
-      <c r="B77" t="s" s="7">
+      <c r="D78" s="8"/>
+      <c r="E78" s="5"/>
+    </row>
+    <row r="79" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="7">
+        <v>24</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C79" s="7">
+        <v>2</v>
+      </c>
+      <c r="D79" s="8"/>
+      <c r="E79" s="5"/>
+    </row>
+    <row r="80" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="8"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C77" s="8">
-        <v>1</v>
-      </c>
-      <c r="D77" s="9"/>
-      <c r="E77" s="5"/>
-    </row>
-    <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="9"/>
-      <c r="B78" s="9"/>
-      <c r="C78" t="s" s="7">
+      <c r="D80" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E80" s="5"/>
+    </row>
+    <row r="81" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="8"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D78" s="9"/>
-      <c r="E78" s="5"/>
-    </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="8">
-        <v>24</v>
-      </c>
-      <c r="B79" t="s" s="7">
-        <v>63</v>
-      </c>
-      <c r="C79" s="8">
+      <c r="D81" s="8"/>
+      <c r="E81" s="5"/>
+    </row>
+    <row r="82" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="7">
+        <v>25</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C82" s="7">
         <v>2</v>
       </c>
-      <c r="D79" s="9"/>
-      <c r="E79" s="5"/>
-    </row>
-    <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="9"/>
-      <c r="B80" s="9"/>
-      <c r="C80" t="s" s="7">
+      <c r="D82" s="8"/>
+      <c r="E82" s="5"/>
+    </row>
+    <row r="83" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="8"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="D80" t="s" s="7">
-        <v>146</v>
-      </c>
-      <c r="E80" s="5"/>
-    </row>
-    <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" t="s" s="7">
+      <c r="D83" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E83" s="5"/>
+    </row>
+    <row r="84" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D81" s="9"/>
-      <c r="E81" s="5"/>
-    </row>
-    <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="8">
-        <v>25</v>
-      </c>
-      <c r="B82" t="s" s="7">
-        <v>68</v>
-      </c>
-      <c r="C82" s="8">
+      <c r="D84" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E84" s="5"/>
+    </row>
+    <row r="85" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="7">
+        <v>26</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C85" s="7">
+        <v>3</v>
+      </c>
+      <c r="D85" s="8"/>
+      <c r="E85" s="5"/>
+    </row>
+    <row r="86" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="8"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D86" s="8"/>
+      <c r="E86" s="5"/>
+    </row>
+    <row r="87" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="8"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D87" s="8"/>
+      <c r="E87" s="5"/>
+    </row>
+    <row r="88" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="8"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D88" s="8"/>
+      <c r="E88" s="5"/>
+    </row>
+    <row r="89" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="7">
+        <v>27</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C89" s="7">
+        <v>5</v>
+      </c>
+      <c r="D89" s="8"/>
+      <c r="E89" s="5"/>
+    </row>
+    <row r="90" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="8"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D90" s="8"/>
+      <c r="E90" s="5"/>
+    </row>
+    <row r="91" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="8"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D91" s="8"/>
+      <c r="E91" s="5"/>
+    </row>
+    <row r="92" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="8"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D92" s="8"/>
+      <c r="E92" s="5"/>
+    </row>
+    <row r="93" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="8"/>
+      <c r="B93" s="8"/>
+      <c r="C93" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D93" s="8"/>
+      <c r="E93" s="5"/>
+    </row>
+    <row r="94" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="8"/>
+      <c r="B94" s="8"/>
+      <c r="C94" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D94" s="8"/>
+      <c r="E94" s="5"/>
+    </row>
+    <row r="95" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="7">
+        <v>28</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C95" s="7">
+        <v>1</v>
+      </c>
+      <c r="D95" s="8"/>
+      <c r="E95" s="5"/>
+    </row>
+    <row r="96" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="8"/>
+      <c r="B96" s="8"/>
+      <c r="C96" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D96" s="8"/>
+      <c r="E96" s="5"/>
+    </row>
+    <row r="97" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="7">
+        <v>29</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C97" s="7">
+        <v>1</v>
+      </c>
+      <c r="D97" s="8"/>
+      <c r="E97" s="5"/>
+    </row>
+    <row r="98" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="8"/>
+      <c r="B98" s="8"/>
+      <c r="C98" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D98" s="8"/>
+      <c r="E98" s="5"/>
+    </row>
+    <row r="99" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="11">
+        <v>30</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C99" s="7">
+        <v>1</v>
+      </c>
+      <c r="D99" s="8"/>
+      <c r="E99" s="5"/>
+    </row>
+    <row r="100" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="8"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D100" s="8"/>
+      <c r="E100" s="5"/>
+    </row>
+    <row r="101" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="11">
+        <v>31</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C101" s="3">
+        <v>1</v>
+      </c>
+      <c r="D101" s="8"/>
+      <c r="E101" s="5"/>
+    </row>
+    <row r="102" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="8"/>
+      <c r="B102" s="8"/>
+      <c r="C102" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D102" s="8"/>
+      <c r="E102" s="5"/>
+    </row>
+    <row r="103" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="7">
+        <v>32</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C103" s="3">
+        <v>1</v>
+      </c>
+      <c r="D103" s="8"/>
+      <c r="E103" s="5"/>
+    </row>
+    <row r="104" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="9"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="D104" s="8"/>
+      <c r="E104" s="5"/>
+    </row>
+    <row r="105" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="7">
+        <v>33</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C105" s="7">
+        <v>5</v>
+      </c>
+      <c r="D105" s="8"/>
+      <c r="E105" s="5"/>
+    </row>
+    <row r="106" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="8"/>
+      <c r="B106" s="8"/>
+      <c r="C106" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D106" s="8"/>
+      <c r="E106" s="5"/>
+    </row>
+    <row r="107" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="8"/>
+      <c r="B107" s="8"/>
+      <c r="C107" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D107" s="8"/>
+      <c r="E107" s="5"/>
+    </row>
+    <row r="108" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="8"/>
+      <c r="B108" s="8"/>
+      <c r="C108" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="D108" s="8"/>
+      <c r="E108" s="5"/>
+    </row>
+    <row r="109" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="8"/>
+      <c r="B109" s="8"/>
+      <c r="C109" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="D109" s="8"/>
+      <c r="E109" s="5"/>
+    </row>
+    <row r="110" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="8"/>
+      <c r="B110" s="8"/>
+      <c r="C110" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D110" s="8"/>
+      <c r="E110" s="5"/>
+    </row>
+    <row r="111" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="7">
+        <v>34</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C111" s="7">
+        <v>1</v>
+      </c>
+      <c r="D111" s="8"/>
+      <c r="E111" s="5"/>
+    </row>
+    <row r="112" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="8"/>
+      <c r="B112" s="8"/>
+      <c r="C112" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="D112" s="8"/>
+      <c r="E112" s="5"/>
+    </row>
+    <row r="113" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="7">
+        <v>35</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C113" s="7">
+        <v>5</v>
+      </c>
+      <c r="D113" s="8"/>
+      <c r="E113" s="5"/>
+    </row>
+    <row r="114" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="8"/>
+      <c r="B114" s="8"/>
+      <c r="C114" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E114" s="5"/>
+    </row>
+    <row r="115" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="8"/>
+      <c r="B115" s="8"/>
+      <c r="C115" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E115" s="5"/>
+    </row>
+    <row r="116" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="8"/>
+      <c r="B116" s="8"/>
+      <c r="C116" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="D116" s="8"/>
+      <c r="E116" s="5"/>
+    </row>
+    <row r="117" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="8"/>
+      <c r="B117" s="8"/>
+      <c r="C117" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E117" s="5"/>
+    </row>
+    <row r="118" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="8"/>
+      <c r="B118" s="8"/>
+      <c r="C118" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E118" s="5"/>
+    </row>
+    <row r="119" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="7">
+        <v>36</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C119" s="7">
+        <v>4</v>
+      </c>
+      <c r="D119" s="8"/>
+      <c r="E119" s="5"/>
+    </row>
+    <row r="120" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="8"/>
+      <c r="B120" s="8"/>
+      <c r="C120" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="D120" s="8"/>
+      <c r="E120" s="5"/>
+    </row>
+    <row r="121" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="8"/>
+      <c r="B121" s="8"/>
+      <c r="C121" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D121" s="8"/>
+      <c r="E121" s="5"/>
+    </row>
+    <row r="122" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="8"/>
+      <c r="B122" s="8"/>
+      <c r="C122" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="D122" s="8"/>
+      <c r="E122" s="5"/>
+    </row>
+    <row r="123" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="8"/>
+      <c r="B123" s="8"/>
+      <c r="C123" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D123" s="8"/>
+      <c r="E123" s="5"/>
+    </row>
+    <row r="124" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="7">
+        <v>37</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C124" s="7">
+        <v>1</v>
+      </c>
+      <c r="D124" s="8"/>
+      <c r="E124" s="5"/>
+    </row>
+    <row r="125" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="8"/>
+      <c r="B125" s="8"/>
+      <c r="C125" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="D125" s="8"/>
+      <c r="E125" s="5"/>
+    </row>
+    <row r="126" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="7">
+        <v>38</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C126" s="16">
+        <v>3</v>
+      </c>
+      <c r="D126" s="8"/>
+      <c r="E126" s="5"/>
+    </row>
+    <row r="127" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="8"/>
+      <c r="B127" s="8"/>
+      <c r="C127" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="D127" s="8"/>
+      <c r="E127" s="5"/>
+    </row>
+    <row r="128" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="8"/>
+      <c r="B128" s="8"/>
+      <c r="C128" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D128" s="8"/>
+      <c r="E128" s="5"/>
+    </row>
+    <row r="129" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="8"/>
+      <c r="B129" s="8"/>
+      <c r="C129" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="D129" s="8"/>
+      <c r="E129" s="5"/>
+    </row>
+    <row r="130" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="7">
+        <v>39</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C130" s="7">
+        <v>5</v>
+      </c>
+      <c r="D130" s="8"/>
+      <c r="E130" s="5"/>
+    </row>
+    <row r="131" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="8"/>
+      <c r="B131" s="8"/>
+      <c r="C131" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="D131" s="8"/>
+      <c r="E131" s="5"/>
+    </row>
+    <row r="132" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="8"/>
+      <c r="B132" s="8"/>
+      <c r="C132" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D132" s="8"/>
+      <c r="E132" s="5"/>
+    </row>
+    <row r="133" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="8"/>
+      <c r="B133" s="8"/>
+      <c r="C133" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E133" s="5"/>
+    </row>
+    <row r="134" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="8"/>
+      <c r="B134" s="8"/>
+      <c r="C134" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D134" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E134" s="5"/>
+    </row>
+    <row r="135" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="8"/>
+      <c r="B135" s="8"/>
+      <c r="C135" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D135" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E135" s="5"/>
+    </row>
+    <row r="136" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="7">
+        <v>40</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C136" s="7">
+        <v>1</v>
+      </c>
+      <c r="D136" s="8"/>
+      <c r="E136" s="5"/>
+    </row>
+    <row r="137" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="8"/>
+      <c r="B137" s="8"/>
+      <c r="C137" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="D137" s="8"/>
+      <c r="E137" s="5"/>
+    </row>
+    <row r="138" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="7">
+        <v>41</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C138" s="7">
+        <v>1</v>
+      </c>
+      <c r="D138" s="8"/>
+      <c r="E138" s="5"/>
+    </row>
+    <row r="139" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="8"/>
+      <c r="B139" s="8"/>
+      <c r="C139" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D139" s="8"/>
+      <c r="E139" s="5"/>
+    </row>
+    <row r="140" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="17">
+        <v>42</v>
+      </c>
+      <c r="B140" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C140" s="19">
+        <v>1</v>
+      </c>
+      <c r="D140" s="20"/>
+      <c r="E140" s="21"/>
+    </row>
+    <row r="141" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="22"/>
+      <c r="B141" s="23"/>
+      <c r="C141" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="D141" s="23"/>
+      <c r="E141" s="25"/>
+    </row>
+    <row r="142" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="7">
+        <v>43</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C142" s="7">
         <v>2</v>
       </c>
-      <c r="D82" s="9"/>
-      <c r="E82" s="5"/>
-    </row>
-    <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="9"/>
-      <c r="B83" s="9"/>
-      <c r="C83" t="s" s="7">
-        <v>196</v>
-      </c>
-      <c r="D83" t="s" s="7">
-        <v>146</v>
-      </c>
-      <c r="E83" s="5"/>
-    </row>
-    <row r="84" ht="17" customHeight="1">
-      <c r="A84" s="9"/>
-      <c r="B84" s="9"/>
-      <c r="C84" t="s" s="7">
-        <v>197</v>
-      </c>
-      <c r="D84" t="s" s="7">
-        <v>146</v>
-      </c>
-      <c r="E84" s="5"/>
-    </row>
-    <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="8">
-        <v>26</v>
-      </c>
-      <c r="B85" t="s" s="7">
-        <v>72</v>
-      </c>
-      <c r="C85" s="8">
-        <v>3</v>
-      </c>
-      <c r="D85" s="9"/>
-      <c r="E85" s="5"/>
-    </row>
-    <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="9"/>
-      <c r="B86" s="9"/>
-      <c r="C86" t="s" s="7">
-        <v>198</v>
-      </c>
-      <c r="D86" s="9"/>
-      <c r="E86" s="5"/>
-    </row>
-    <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="9"/>
-      <c r="B87" s="9"/>
-      <c r="C87" t="s" s="7">
-        <v>199</v>
-      </c>
-      <c r="D87" s="9"/>
-      <c r="E87" s="5"/>
-    </row>
-    <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="9"/>
-      <c r="B88" s="9"/>
-      <c r="C88" t="s" s="7">
-        <v>200</v>
-      </c>
-      <c r="D88" s="9"/>
-      <c r="E88" s="5"/>
-    </row>
-    <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="8">
-        <v>27</v>
-      </c>
-      <c r="B89" t="s" s="7">
-        <v>76</v>
-      </c>
-      <c r="C89" s="8">
-        <v>5</v>
-      </c>
-      <c r="D89" s="9"/>
-      <c r="E89" s="5"/>
-    </row>
-    <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="9"/>
-      <c r="B90" s="9"/>
-      <c r="C90" t="s" s="7">
-        <v>201</v>
-      </c>
-      <c r="D90" s="9"/>
-      <c r="E90" s="5"/>
-    </row>
-    <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="9"/>
-      <c r="B91" s="9"/>
-      <c r="C91" t="s" s="7">
-        <v>202</v>
-      </c>
-      <c r="D91" s="9"/>
-      <c r="E91" s="5"/>
-    </row>
-    <row r="92" ht="17" customHeight="1">
-      <c r="A92" s="9"/>
-      <c r="B92" s="9"/>
-      <c r="C92" t="s" s="7">
-        <v>203</v>
-      </c>
-      <c r="D92" s="9"/>
-      <c r="E92" s="5"/>
-    </row>
-    <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="9"/>
-      <c r="B93" s="9"/>
-      <c r="C93" t="s" s="7">
-        <v>204</v>
-      </c>
-      <c r="D93" s="9"/>
-      <c r="E93" s="5"/>
-    </row>
-    <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="9"/>
-      <c r="B94" s="9"/>
-      <c r="C94" t="s" s="7">
-        <v>205</v>
-      </c>
-      <c r="D94" s="9"/>
-      <c r="E94" s="5"/>
-    </row>
-    <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="8">
-        <v>28</v>
-      </c>
-      <c r="B95" t="s" s="7">
-        <v>80</v>
-      </c>
-      <c r="C95" s="8">
-        <v>1</v>
-      </c>
-      <c r="D95" s="9"/>
-      <c r="E95" s="5"/>
-    </row>
-    <row r="96" ht="17" customHeight="1">
-      <c r="A96" s="9"/>
-      <c r="B96" s="9"/>
-      <c r="C96" t="s" s="7">
-        <v>206</v>
-      </c>
-      <c r="D96" s="9"/>
-      <c r="E96" s="5"/>
-    </row>
-    <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="8">
-        <v>29</v>
-      </c>
-      <c r="B97" t="s" s="7">
-        <v>82</v>
-      </c>
-      <c r="C97" s="8">
-        <v>1</v>
-      </c>
-      <c r="D97" s="9"/>
-      <c r="E97" s="5"/>
-    </row>
-    <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="9"/>
-      <c r="B98" s="9"/>
-      <c r="C98" t="s" s="7">
-        <v>207</v>
-      </c>
-      <c r="D98" s="9"/>
-      <c r="E98" s="5"/>
-    </row>
-    <row r="99" ht="17" customHeight="1">
-      <c r="A99" s="12">
-        <v>30</v>
-      </c>
-      <c r="B99" t="s" s="13">
-        <v>86</v>
-      </c>
-      <c r="C99" s="8">
-        <v>1</v>
-      </c>
-      <c r="D99" s="9"/>
-      <c r="E99" s="5"/>
-    </row>
-    <row r="100" ht="17" customHeight="1">
-      <c r="A100" s="9"/>
-      <c r="B100" s="9"/>
-      <c r="C100" t="s" s="7">
-        <v>208</v>
-      </c>
-      <c r="D100" s="9"/>
-      <c r="E100" s="5"/>
-    </row>
-    <row r="101" ht="17" customHeight="1">
-      <c r="A101" s="12">
-        <v>31</v>
-      </c>
-      <c r="B101" t="s" s="13">
-        <v>87</v>
-      </c>
-      <c r="C101" s="3">
-        <v>1</v>
-      </c>
-      <c r="D101" s="9"/>
-      <c r="E101" s="5"/>
-    </row>
-    <row r="102" ht="17" customHeight="1">
-      <c r="A102" s="9"/>
-      <c r="B102" s="9"/>
-      <c r="C102" t="s" s="11">
-        <v>209</v>
-      </c>
-      <c r="D102" s="9"/>
-      <c r="E102" s="5"/>
-    </row>
-    <row r="103" ht="17" customHeight="1">
-      <c r="A103" s="8">
-        <v>32</v>
-      </c>
-      <c r="B103" t="s" s="7">
-        <v>90</v>
-      </c>
-      <c r="C103" s="3">
-        <v>1</v>
-      </c>
-      <c r="D103" s="9"/>
-      <c r="E103" s="5"/>
-    </row>
-    <row r="104" ht="17" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="7"/>
-      <c r="C104" t="s" s="16">
-        <v>210</v>
-      </c>
-      <c r="D104" s="9"/>
-      <c r="E104" s="5"/>
-    </row>
-    <row r="105" ht="17" customHeight="1">
-      <c r="A105" s="8">
-        <v>33</v>
-      </c>
-      <c r="B105" t="s" s="7">
-        <v>211</v>
-      </c>
-      <c r="C105" s="8">
-        <v>5</v>
-      </c>
-      <c r="D105" s="9"/>
-      <c r="E105" s="5"/>
-    </row>
-    <row r="106" ht="17" customHeight="1">
-      <c r="A106" s="9"/>
-      <c r="B106" s="9"/>
-      <c r="C106" t="s" s="11">
-        <v>212</v>
-      </c>
-      <c r="D106" s="9"/>
-      <c r="E106" s="5"/>
-    </row>
-    <row r="107" ht="17" customHeight="1">
-      <c r="A107" s="9"/>
-      <c r="B107" s="9"/>
-      <c r="C107" t="s" s="11">
-        <v>213</v>
-      </c>
-      <c r="D107" s="9"/>
-      <c r="E107" s="5"/>
-    </row>
-    <row r="108" ht="17" customHeight="1">
-      <c r="A108" s="9"/>
-      <c r="B108" s="9"/>
-      <c r="C108" t="s" s="11">
-        <v>214</v>
-      </c>
-      <c r="D108" s="9"/>
-      <c r="E108" s="5"/>
-    </row>
-    <row r="109" ht="17" customHeight="1">
-      <c r="A109" s="9"/>
-      <c r="B109" s="9"/>
-      <c r="C109" t="s" s="11">
-        <v>215</v>
-      </c>
-      <c r="D109" s="9"/>
-      <c r="E109" s="5"/>
-    </row>
-    <row r="110" ht="17" customHeight="1">
-      <c r="A110" s="9"/>
-      <c r="B110" s="9"/>
-      <c r="C110" t="s" s="11">
-        <v>216</v>
-      </c>
-      <c r="D110" s="9"/>
-      <c r="E110" s="5"/>
-    </row>
-    <row r="111" ht="17" customHeight="1">
-      <c r="A111" s="8">
-        <v>34</v>
-      </c>
-      <c r="B111" t="s" s="7">
-        <v>217</v>
-      </c>
-      <c r="C111" s="8">
-        <v>1</v>
-      </c>
-      <c r="D111" s="9"/>
-      <c r="E111" s="5"/>
-    </row>
-    <row r="112" ht="17" customHeight="1">
-      <c r="A112" s="9"/>
-      <c r="B112" s="9"/>
-      <c r="C112" t="s" s="11">
-        <v>218</v>
-      </c>
-      <c r="D112" s="9"/>
-      <c r="E112" s="5"/>
-    </row>
-    <row r="113" ht="17" customHeight="1">
-      <c r="A113" s="8">
-        <v>35</v>
-      </c>
-      <c r="B113" t="s" s="7">
-        <v>94</v>
-      </c>
-      <c r="C113" s="8">
-        <v>5</v>
-      </c>
-      <c r="D113" s="9"/>
-      <c r="E113" s="5"/>
-    </row>
-    <row r="114" ht="17" customHeight="1">
-      <c r="A114" s="9"/>
-      <c r="B114" s="9"/>
-      <c r="C114" t="s" s="11">
-        <v>219</v>
-      </c>
-      <c r="D114" t="s" s="7">
-        <v>220</v>
-      </c>
-      <c r="E114" s="5"/>
-    </row>
-    <row r="115" ht="17" customHeight="1">
-      <c r="A115" s="9"/>
-      <c r="B115" s="9"/>
-      <c r="C115" t="s" s="11">
-        <v>221</v>
-      </c>
-      <c r="D115" t="s" s="7">
-        <v>220</v>
-      </c>
-      <c r="E115" s="5"/>
-    </row>
-    <row r="116" ht="17" customHeight="1">
-      <c r="A116" s="9"/>
-      <c r="B116" s="9"/>
-      <c r="C116" t="s" s="11">
-        <v>222</v>
-      </c>
-      <c r="D116" s="9"/>
-      <c r="E116" s="5"/>
-    </row>
-    <row r="117" ht="17" customHeight="1">
-      <c r="A117" s="9"/>
-      <c r="B117" s="9"/>
-      <c r="C117" t="s" s="11">
-        <v>223</v>
-      </c>
-      <c r="D117" t="s" s="7">
-        <v>146</v>
-      </c>
-      <c r="E117" s="5"/>
-    </row>
-    <row r="118" ht="17" customHeight="1">
-      <c r="A118" s="9"/>
-      <c r="B118" s="9"/>
-      <c r="C118" t="s" s="11">
-        <v>224</v>
-      </c>
-      <c r="D118" t="s" s="7">
-        <v>225</v>
-      </c>
-      <c r="E118" s="5"/>
-    </row>
-    <row r="119" ht="17" customHeight="1">
-      <c r="A119" s="8">
-        <v>36</v>
-      </c>
-      <c r="B119" t="s" s="7">
-        <v>95</v>
-      </c>
-      <c r="C119" s="8">
-        <v>4</v>
-      </c>
-      <c r="D119" s="9"/>
-      <c r="E119" s="5"/>
-    </row>
-    <row r="120" ht="17" customHeight="1">
-      <c r="A120" s="9"/>
-      <c r="B120" s="9"/>
-      <c r="C120" t="s" s="11">
-        <v>226</v>
-      </c>
-      <c r="D120" s="9"/>
-      <c r="E120" s="5"/>
-    </row>
-    <row r="121" ht="17" customHeight="1">
-      <c r="A121" s="9"/>
-      <c r="B121" s="9"/>
-      <c r="C121" t="s" s="11">
-        <v>227</v>
-      </c>
-      <c r="D121" s="9"/>
-      <c r="E121" s="5"/>
-    </row>
-    <row r="122" ht="17" customHeight="1">
-      <c r="A122" s="9"/>
-      <c r="B122" s="9"/>
-      <c r="C122" t="s" s="11">
-        <v>228</v>
-      </c>
-      <c r="D122" s="9"/>
-      <c r="E122" s="5"/>
-    </row>
-    <row r="123" ht="17" customHeight="1">
-      <c r="A123" s="9"/>
-      <c r="B123" s="9"/>
-      <c r="C123" t="s" s="11">
-        <v>229</v>
-      </c>
-      <c r="D123" s="9"/>
-      <c r="E123" s="5"/>
-    </row>
-    <row r="124" ht="17" customHeight="1">
-      <c r="A124" s="8">
-        <v>37</v>
-      </c>
-      <c r="B124" t="s" s="7">
-        <v>96</v>
-      </c>
-      <c r="C124" s="8">
-        <v>1</v>
-      </c>
-      <c r="D124" s="9"/>
-      <c r="E124" s="5"/>
-    </row>
-    <row r="125" ht="17" customHeight="1">
-      <c r="A125" s="9"/>
-      <c r="B125" s="9"/>
-      <c r="C125" t="s" s="11">
-        <v>230</v>
-      </c>
-      <c r="D125" s="9"/>
-      <c r="E125" s="5"/>
-    </row>
-    <row r="126" ht="17" customHeight="1">
-      <c r="A126" s="8">
-        <v>38</v>
-      </c>
-      <c r="B126" t="s" s="7">
-        <v>98</v>
-      </c>
-      <c r="C126" s="17">
-        <v>3</v>
-      </c>
-      <c r="D126" s="9"/>
-      <c r="E126" s="5"/>
-    </row>
-    <row r="127" ht="15" customHeight="1">
-      <c r="A127" s="9"/>
-      <c r="B127" s="9"/>
-      <c r="C127" t="s" s="11">
-        <v>231</v>
-      </c>
-      <c r="D127" s="9"/>
-      <c r="E127" s="5"/>
-    </row>
-    <row r="128" ht="15" customHeight="1">
-      <c r="A128" s="9"/>
-      <c r="B128" s="9"/>
-      <c r="C128" t="s" s="11">
-        <v>232</v>
-      </c>
-      <c r="D128" s="9"/>
-      <c r="E128" s="5"/>
-    </row>
-    <row r="129" ht="15" customHeight="1">
-      <c r="A129" s="9"/>
-      <c r="B129" s="9"/>
-      <c r="C129" t="s" s="11">
-        <v>233</v>
-      </c>
-      <c r="D129" s="9"/>
-      <c r="E129" s="5"/>
-    </row>
-    <row r="130" ht="17" customHeight="1">
-      <c r="A130" s="8">
-        <v>39</v>
-      </c>
-      <c r="B130" t="s" s="7">
-        <v>100</v>
-      </c>
-      <c r="C130" s="8">
-        <v>5</v>
-      </c>
-      <c r="D130" s="9"/>
-      <c r="E130" s="5"/>
-    </row>
-    <row r="131" ht="17" customHeight="1">
-      <c r="A131" s="9"/>
-      <c r="B131" s="9"/>
-      <c r="C131" t="s" s="11">
-        <v>234</v>
-      </c>
-      <c r="D131" s="9"/>
-      <c r="E131" s="5"/>
-    </row>
-    <row r="132" ht="17" customHeight="1">
-      <c r="A132" s="9"/>
-      <c r="B132" s="9"/>
-      <c r="C132" t="s" s="11">
-        <v>235</v>
-      </c>
-      <c r="D132" s="9"/>
-      <c r="E132" s="5"/>
-    </row>
-    <row r="133" ht="17" customHeight="1">
-      <c r="A133" s="9"/>
-      <c r="B133" s="9"/>
-      <c r="C133" t="s" s="11">
-        <v>236</v>
-      </c>
-      <c r="D133" t="s" s="11">
-        <v>146</v>
-      </c>
-      <c r="E133" s="5"/>
-    </row>
-    <row r="134" ht="17" customHeight="1">
-      <c r="A134" s="9"/>
-      <c r="B134" s="9"/>
-      <c r="C134" t="s" s="11">
-        <v>237</v>
-      </c>
-      <c r="D134" t="s" s="11">
-        <v>146</v>
-      </c>
-      <c r="E134" s="5"/>
-    </row>
-    <row r="135" ht="17" customHeight="1">
-      <c r="A135" s="9"/>
-      <c r="B135" s="9"/>
-      <c r="C135" t="s" s="11">
-        <v>238</v>
-      </c>
-      <c r="D135" t="s" s="11">
-        <v>146</v>
-      </c>
-      <c r="E135" s="5"/>
-    </row>
-    <row r="136" ht="17" customHeight="1">
-      <c r="A136" s="8">
-        <v>40</v>
-      </c>
-      <c r="B136" t="s" s="7">
-        <v>101</v>
-      </c>
-      <c r="C136" s="8">
-        <v>1</v>
-      </c>
-      <c r="D136" s="9"/>
-      <c r="E136" s="5"/>
-    </row>
-    <row r="137" ht="17" customHeight="1">
-      <c r="A137" s="9"/>
-      <c r="B137" s="9"/>
-      <c r="C137" t="s" s="11">
-        <v>239</v>
-      </c>
-      <c r="D137" s="9"/>
-      <c r="E137" s="5"/>
-    </row>
-    <row r="138" ht="17" customHeight="1">
-      <c r="A138" s="8">
-        <v>41</v>
-      </c>
-      <c r="B138" t="s" s="7">
-        <v>240</v>
-      </c>
-      <c r="C138" s="8">
-        <v>1</v>
-      </c>
-      <c r="D138" s="9"/>
-      <c r="E138" s="5"/>
-    </row>
-    <row r="139" ht="17" customHeight="1">
-      <c r="A139" s="9"/>
-      <c r="B139" s="9"/>
-      <c r="C139" t="s" s="11">
+      <c r="D142" s="8"/>
+      <c r="E142" s="5"/>
+    </row>
+    <row r="143" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="8"/>
+      <c r="B143" s="8"/>
+      <c r="C143" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="D139" s="9"/>
-      <c r="E139" s="5"/>
-    </row>
-    <row r="140" ht="17" customHeight="1">
-      <c r="A140" s="18">
-        <v>42</v>
-      </c>
-      <c r="B140" t="s" s="19">
-        <v>108</v>
-      </c>
-      <c r="C140" s="20">
-        <v>1</v>
-      </c>
-      <c r="D140" s="21"/>
-      <c r="E140" s="22"/>
-    </row>
-    <row r="141" ht="17" customHeight="1">
-      <c r="A141" s="23"/>
-      <c r="B141" s="24"/>
-      <c r="C141" t="s" s="25">
+      <c r="D143" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E143" s="5"/>
+    </row>
+    <row r="144" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="8"/>
+      <c r="B144" s="8"/>
+      <c r="C144" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="D141" s="24"/>
-      <c r="E141" s="26"/>
-    </row>
-    <row r="142" ht="17" customHeight="1">
-      <c r="A142" s="8">
-        <v>43</v>
-      </c>
-      <c r="B142" t="s" s="7">
-        <v>112</v>
-      </c>
-      <c r="C142" s="8">
+      <c r="D144" s="8"/>
+      <c r="E144" s="5"/>
+    </row>
+    <row r="145" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="7">
+        <v>44</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C145" s="7">
+        <v>1</v>
+      </c>
+      <c r="D145" s="8"/>
+      <c r="E145" s="5"/>
+    </row>
+    <row r="146" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="8"/>
+      <c r="B146" s="8"/>
+      <c r="C146" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D146" s="8"/>
+      <c r="E146" s="5"/>
+    </row>
+    <row r="147" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="7">
+        <v>45</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C147" s="7">
         <v>2</v>
       </c>
-      <c r="D142" s="9"/>
-      <c r="E142" s="5"/>
-    </row>
-    <row r="143" ht="17" customHeight="1">
-      <c r="A143" s="9"/>
-      <c r="B143" s="9"/>
-      <c r="C143" t="s" s="7">
-        <v>243</v>
-      </c>
-      <c r="D143" t="s" s="7">
-        <v>146</v>
-      </c>
-      <c r="E143" s="5"/>
-    </row>
-    <row r="144" ht="17" customHeight="1">
-      <c r="A144" s="9"/>
-      <c r="B144" s="9"/>
-      <c r="C144" t="s" s="7">
-        <v>244</v>
-      </c>
-      <c r="D144" s="9"/>
-      <c r="E144" s="5"/>
-    </row>
-    <row r="145" ht="17" customHeight="1">
-      <c r="A145" s="8">
-        <v>44</v>
-      </c>
-      <c r="B145" t="s" s="7">
-        <v>116</v>
-      </c>
-      <c r="C145" s="8">
-        <v>1</v>
-      </c>
-      <c r="D145" s="9"/>
-      <c r="E145" s="5"/>
-    </row>
-    <row r="146" ht="17" customHeight="1">
-      <c r="A146" s="9"/>
-      <c r="B146" s="9"/>
-      <c r="C146" t="s" s="7">
+      <c r="D147" s="8"/>
+      <c r="E147" s="5"/>
+    </row>
+    <row r="148" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="8"/>
+      <c r="B148" s="8"/>
+      <c r="C148" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D146" s="9"/>
-      <c r="E146" s="5"/>
-    </row>
-    <row r="147" ht="17" customHeight="1">
-      <c r="A147" s="8">
-        <v>45</v>
-      </c>
-      <c r="B147" t="s" s="7">
+      <c r="D148" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E148" s="5"/>
+    </row>
+    <row r="149" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="8"/>
+      <c r="B149" s="8"/>
+      <c r="C149" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="C147" s="8">
-        <v>2</v>
-      </c>
-      <c r="D147" s="9"/>
-      <c r="E147" s="5"/>
-    </row>
-    <row r="148" ht="17" customHeight="1">
-      <c r="A148" s="9"/>
-      <c r="B148" s="9"/>
-      <c r="C148" t="s" s="7">
+      <c r="D149" s="8"/>
+      <c r="E149" s="5"/>
+    </row>
+    <row r="150" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="7">
+        <v>46</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C150" s="7">
+        <v>1</v>
+      </c>
+      <c r="D150" s="8"/>
+      <c r="E150" s="5"/>
+    </row>
+    <row r="151" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="8"/>
+      <c r="B151" s="8"/>
+      <c r="C151" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="D148" t="s" s="7">
-        <v>146</v>
-      </c>
-      <c r="E148" s="5"/>
-    </row>
-    <row r="149" ht="17" customHeight="1">
-      <c r="A149" s="9"/>
-      <c r="B149" s="9"/>
-      <c r="C149" t="s" s="7">
-        <v>248</v>
-      </c>
-      <c r="D149" s="9"/>
-      <c r="E149" s="5"/>
-    </row>
-    <row r="150" ht="17" customHeight="1">
-      <c r="A150" s="8">
-        <v>46</v>
-      </c>
-      <c r="B150" t="s" s="7">
-        <v>124</v>
-      </c>
-      <c r="C150" s="8">
-        <v>1</v>
-      </c>
-      <c r="D150" s="9"/>
-      <c r="E150" s="5"/>
-    </row>
-    <row r="151" ht="17" customHeight="1">
-      <c r="A151" s="9"/>
-      <c r="B151" s="9"/>
-      <c r="C151" t="s" s="7">
-        <v>249</v>
-      </c>
-      <c r="D151" t="s" s="7">
-        <v>146</v>
+      <c r="D151" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="E151" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C34:D34"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
